--- a/docs/LegacyNest_Project_Plan.xlsx
+++ b/docs/LegacyNest_Project_Plan.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="143">
   <si>
     <t>Milestone</t>
   </si>
@@ -48,7 +48,7 @@
     <t>In progress</t>
   </si>
   <si>
-    <t>Closest to launch; stabilization not features</t>
+    <t>Internally ready ~25 Jul; folds into the 15 Aug public launch</t>
   </si>
   <si>
     <t>M2 — Full product</t>
@@ -60,7 +60,7 @@
     <t>Not started</t>
   </si>
   <si>
-    <t>Ships on current single-child model except coordinator login</t>
+    <t>PUBLIC LAUNCH 15 Aug (Independence Day). Date-driven: cut scope, not the date</t>
   </si>
   <si>
     <t>M3 — Version 2</t>
@@ -72,7 +72,7 @@
     <t>Design locked</t>
   </si>
   <si>
-    <t>Build not started; 8 phases; XL effort</t>
+    <t>Post-launch track; 8 phases; Razorpay deferred until pricing turns on</t>
   </si>
   <si>
     <t>Ref</t>
@@ -93,6 +93,9 @@
     <t>Launch gate</t>
   </si>
   <si>
+    <t>15-Aug scope</t>
+  </si>
+  <si>
     <t>% Complete</t>
   </si>
   <si>
@@ -177,7 +180,7 @@
     <t>Terms of Service + Privacy Policy pages</t>
   </si>
   <si>
-    <t>DPDP / SPDI compliant public legal pages</t>
+    <t>DPDP / SPDI compliant public legal pages (start early - external turnaround)</t>
   </si>
   <si>
     <t>Legal</t>
@@ -231,6 +234,15 @@
     <t>Product</t>
   </si>
   <si>
+    <t>M2-4</t>
+  </si>
+  <si>
+    <t>Restructure landing</t>
+  </si>
+  <si>
+    <t>Quick emergency path vs full plan</t>
+  </si>
+  <si>
     <t>M2-2</t>
   </si>
   <si>
@@ -246,16 +258,7 @@
     <t>"You're ready" wallet card</t>
   </si>
   <si>
-    <t>jspdf/html2canvas, minimal PII, QR -&gt; tokenized URL</t>
-  </si>
-  <si>
-    <t>M2-4</t>
-  </si>
-  <si>
-    <t>Restructure landing</t>
-  </si>
-  <si>
-    <t>Quick emergency path vs full plan</t>
+    <t>jspdf/html2canvas, minimal PII, QR -&gt; tokenized URL (first to cut if slipping)</t>
   </si>
   <si>
     <t>M2-5</t>
@@ -264,7 +267,7 @@
     <t>Free-flow time instrumentation</t>
   </si>
   <si>
-    <t>Track time-to-complete; alert if &gt; 12-15 min</t>
+    <t>Track time-to-complete; alert if &gt; 12-15 min (first to cut if slipping)</t>
   </si>
   <si>
     <t>M2-6</t>
@@ -276,6 +279,9 @@
     <t>In-app raise; depends on v2 role model</t>
   </si>
   <si>
+    <t>Fast-follow</t>
+  </si>
+  <si>
     <t>Blocked</t>
   </si>
   <si>
@@ -366,28 +372,34 @@
     <t>Meaning</t>
   </si>
   <si>
-    <t>Effort — S</t>
-  </si>
-  <si>
-    <t>Small: hours to ~1 day</t>
-  </si>
-  <si>
-    <t>Effort — M</t>
-  </si>
-  <si>
-    <t>Medium: a few days</t>
-  </si>
-  <si>
-    <t>Effort — L</t>
-  </si>
-  <si>
-    <t>Large: 1-2 weeks</t>
-  </si>
-  <si>
-    <t>Effort — XL</t>
-  </si>
-  <si>
-    <t>Extra large: multi-week</t>
+    <t>KEY DATE — 15 Aug 2026</t>
+  </si>
+  <si>
+    <t>Public launch (Independence Day) = M1 + the M2 free emergency wedge. Date-driven: cut scope, not the date.</t>
+  </si>
+  <si>
+    <t>15-Aug scope = Yes</t>
+  </si>
+  <si>
+    <t>Must ship for the 15 Aug launch</t>
+  </si>
+  <si>
+    <t>15-Aug scope = Fast-follow</t>
+  </si>
+  <si>
+    <t>Ships shortly after launch</t>
+  </si>
+  <si>
+    <t>15-Aug scope = No</t>
+  </si>
+  <si>
+    <t>Post-launch (Version 2, Sep-Oct)</t>
+  </si>
+  <si>
+    <t>Effort — S / M / L / XL</t>
+  </si>
+  <si>
+    <t>Small (hrs-1 day) / Medium (days) / Large (1-2 wks) / Extra large (multi-week)</t>
   </si>
   <si>
     <t>Not started / In progress / Blocked / Done</t>
@@ -396,16 +408,16 @@
     <t>Launch gate = Yes</t>
   </si>
   <si>
-    <t>Must be done before public launch</t>
-  </si>
-  <si>
-    <t>The existing full plan, stabilized &amp; legally launchable (free)</t>
-  </si>
-  <si>
-    <t>M1 + the freemium 10-minute emergency wedge</t>
-  </si>
-  <si>
-    <t>Person/child/role redesign, multi-child, subscription infrastructure</t>
+    <t>Hard gate — must be done before any public launch</t>
+  </si>
+  <si>
+    <t>Existing full plan, stabilized &amp; legally launchable (free); internally ready ~25 Jul</t>
+  </si>
+  <si>
+    <t>M1 + the freemium 10-minute emergency wedge; public launch 15 Aug</t>
+  </si>
+  <si>
+    <t>Person/child/role redesign, multi-child, subscription infra; ~late Oct</t>
   </si>
   <si>
     <t>Overdue rows</t>
@@ -423,7 +435,13 @@
     <t>Pricing</t>
   </si>
   <si>
-    <t>Free at launch behind the FREE_LAUNCH flag; only undecided item is the eventual subscription price</t>
+    <t>Free at launch behind the FREE_LAUNCH flag; the eventual subscription price is the only undecided item</t>
+  </si>
+  <si>
+    <t>Pace assumption</t>
+  </si>
+  <si>
+    <t>Dates assume part-time solo + AI. Full-time ~halves the calendar; weekends-only ~1.5-2x.</t>
   </si>
 </sst>
 </file>
@@ -433,7 +451,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd-mmm-yyyy"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -461,8 +479,14 @@
       <sz val="10"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <b/>
+      <color rgb="FFC00000"/>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -472,6 +496,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF4A3728"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F0D9"/>
       </patternFill>
     </fill>
   </fills>
@@ -496,7 +525,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -513,8 +542,13 @@
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -873,11 +907,11 @@
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="2" width="50" customWidth="1"/>
+    <col min="2" max="2" width="48" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
     <col min="4" max="6" width="14" customWidth="1"/>
     <col min="7" max="7" width="16" customWidth="1"/>
-    <col min="8" max="8" width="44" customWidth="1"/>
+    <col min="8" max="8" width="40" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -906,7 +940,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" ht="34" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
@@ -917,11 +951,15 @@
         <v>0.7</v>
       </c>
       <c r="D2" s="5">
-        <f>AVERAGEIF(Tasks!$A$2:$A$23,"M1",Tasks!$I$2:$I$23)</f>
+        <f>AVERAGEIF(Tasks!$A$2:$A$23,"M1",Tasks!$J$2:$J$23)</f>
         <v>0.05</v>
       </c>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
+      <c r="E2" s="6">
+        <v>46203</v>
+      </c>
+      <c r="F2" s="6">
+        <v>46228</v>
+      </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
       </c>
@@ -929,7 +967,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" ht="34" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>12</v>
       </c>
@@ -940,11 +978,15 @@
         <v>0.35</v>
       </c>
       <c r="D3" s="5">
-        <f>AVERAGEIF(Tasks!$A$2:$A$23,"M2",Tasks!$I$2:$I$23)</f>
-        <v>0</v>
-      </c>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
+        <f>AVERAGEIF(Tasks!$A$2:$A$23,"M2",Tasks!$J$2:$J$23)</f>
+        <v>0</v>
+      </c>
+      <c r="E3" s="6">
+        <v>46231</v>
+      </c>
+      <c r="F3" s="6">
+        <v>46249</v>
+      </c>
       <c r="G3" s="3" t="s">
         <v>14</v>
       </c>
@@ -952,7 +994,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" ht="34" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>16</v>
       </c>
@@ -963,11 +1005,15 @@
         <v>0.1</v>
       </c>
       <c r="D4" s="5">
-        <f>AVERAGEIF(Tasks!$A$2:$A$23,"M3",Tasks!$I$2:$I$23)</f>
-        <v>0</v>
-      </c>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
+        <f>AVERAGEIF(Tasks!$A$2:$A$23,"M3",Tasks!$J$2:$J$23)</f>
+        <v>0</v>
+      </c>
+      <c r="E4" s="6">
+        <v>46266</v>
+      </c>
+      <c r="F4" s="6">
+        <v>46319</v>
+      </c>
       <c r="G4" s="3" t="s">
         <v>18</v>
       </c>
@@ -983,24 +1029,25 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O23"/>
+  <dimension ref="A1:P23"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
-    <col min="3" max="3" width="34" customWidth="1"/>
-    <col min="4" max="4" width="50" customWidth="1"/>
+    <col min="3" max="3" width="32" customWidth="1"/>
+    <col min="4" max="4" width="46" customWidth="1"/>
     <col min="5" max="5" width="10" customWidth="1"/>
     <col min="6" max="6" width="8" customWidth="1"/>
-    <col min="7" max="7" width="12" customWidth="1"/>
-    <col min="8" max="8" width="14" customWidth="1"/>
-    <col min="9" max="9" width="11" customWidth="1"/>
-    <col min="10" max="10" width="12" customWidth="1"/>
-    <col min="11" max="13" width="14" customWidth="1"/>
-    <col min="14" max="14" width="16" customWidth="1"/>
-    <col min="15" max="15" width="40" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="13" customWidth="1"/>
+    <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="10" max="10" width="11" customWidth="1"/>
+    <col min="11" max="11" width="12" customWidth="1"/>
+    <col min="12" max="14" width="13" customWidth="1"/>
+    <col min="15" max="15" width="15" customWidth="1"/>
+    <col min="16" max="16" width="36" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" ht="28" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1023,10 +1070,10 @@
         <v>25</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>26</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>27</v>
@@ -1044,831 +1091,980 @@
         <v>31</v>
       </c>
       <c r="O1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="P1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" ht="30" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" ht="30" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J2" s="5">
+        <v>0.4</v>
+      </c>
+      <c r="K2" s="3"/>
+      <c r="L2" s="6">
+        <v>46203</v>
+      </c>
+      <c r="M2" s="6">
+        <v>46205</v>
+      </c>
+      <c r="N2" s="6"/>
+      <c r="O2" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="P2" s="3"/>
+    </row>
+    <row r="3" ht="30" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="B3" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="3"/>
+      <c r="L3" s="6">
+        <v>46204</v>
+      </c>
+      <c r="M3" s="6">
+        <v>46212</v>
+      </c>
+      <c r="N3" s="6"/>
+      <c r="O3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="P3" s="3"/>
+    </row>
+    <row r="4" ht="30" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="3"/>
+      <c r="L4" s="6">
+        <v>46210</v>
+      </c>
+      <c r="M4" s="6">
+        <v>46214</v>
+      </c>
+      <c r="N4" s="6"/>
+      <c r="O4" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F2" s="3" t="s">
+      <c r="P4" s="3"/>
+    </row>
+    <row r="5" ht="30" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="3"/>
+      <c r="L5" s="6">
+        <v>46217</v>
+      </c>
+      <c r="M5" s="6">
+        <v>46221</v>
+      </c>
+      <c r="N5" s="6"/>
+      <c r="O5" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="P5" s="3"/>
+    </row>
+    <row r="6" ht="30" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="3"/>
+      <c r="L6" s="6">
+        <v>46203</v>
+      </c>
+      <c r="M6" s="6">
+        <v>46221</v>
+      </c>
+      <c r="N6" s="6"/>
+      <c r="O6" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="P6" s="3"/>
+    </row>
+    <row r="7" ht="30" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J7" s="5">
+        <v>0</v>
+      </c>
+      <c r="K7" s="3"/>
+      <c r="L7" s="6">
+        <v>46224</v>
+      </c>
+      <c r="M7" s="6">
+        <v>46225</v>
+      </c>
+      <c r="N7" s="6"/>
+      <c r="O7" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="P7" s="3"/>
+    </row>
+    <row r="8" ht="30" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J8" s="5">
+        <v>0</v>
+      </c>
+      <c r="K8" s="3"/>
+      <c r="L8" s="6">
+        <v>46226</v>
+      </c>
+      <c r="M8" s="6">
+        <v>46228</v>
+      </c>
+      <c r="N8" s="6"/>
+      <c r="O8" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="P8" s="3"/>
+    </row>
+    <row r="9" ht="30" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E9" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="F9" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="H2" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="I2" s="5">
-        <v>0.4</v>
-      </c>
-      <c r="J2" s="3"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="3" t="s">
+      <c r="G9" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="O2" s="3"/>
-    </row>
-    <row r="3" ht="30" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B3" s="2" t="s">
+      <c r="H9" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J9" s="5">
+        <v>0</v>
+      </c>
+      <c r="K9" s="3"/>
+      <c r="L9" s="6">
+        <v>46203</v>
+      </c>
+      <c r="M9" s="6">
+        <v>46204</v>
+      </c>
+      <c r="N9" s="6"/>
+      <c r="O9" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="G3" s="3" t="s">
+      <c r="P9" s="3"/>
+    </row>
+    <row r="10" ht="30" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J10" s="5">
+        <v>0</v>
+      </c>
+      <c r="K10" s="3"/>
+      <c r="L10" s="6">
+        <v>46231</v>
+      </c>
+      <c r="M10" s="6">
+        <v>46235</v>
+      </c>
+      <c r="N10" s="6"/>
+      <c r="O10" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="P10" s="3"/>
+    </row>
+    <row r="11" ht="30" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F11" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="G11" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="I11" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="3"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="7"/>
-      <c r="M3" s="7"/>
-      <c r="N3" s="3" t="s">
+      <c r="J11" s="5">
+        <v>0</v>
+      </c>
+      <c r="K11" s="3"/>
+      <c r="L11" s="6">
+        <v>46231</v>
+      </c>
+      <c r="M11" s="6">
+        <v>46233</v>
+      </c>
+      <c r="N11" s="6"/>
+      <c r="O11" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" ht="30" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H12" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="O3" s="3"/>
-    </row>
-    <row r="4" ht="30" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B4" s="2" t="s">
+      <c r="I12" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J12" s="5">
+        <v>0</v>
+      </c>
+      <c r="K12" s="3"/>
+      <c r="L12" s="6">
+        <v>46238</v>
+      </c>
+      <c r="M12" s="6">
+        <v>46242</v>
+      </c>
+      <c r="N12" s="6"/>
+      <c r="O12" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="P12" s="3"/>
+    </row>
+    <row r="13" ht="30" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="F13" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="G4" s="3" t="s">
+      <c r="G13" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J13" s="5">
+        <v>0</v>
+      </c>
+      <c r="K13" s="3"/>
+      <c r="L13" s="6">
+        <v>46241</v>
+      </c>
+      <c r="M13" s="6">
+        <v>46245</v>
+      </c>
+      <c r="N13" s="6"/>
+      <c r="O13" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="P13" s="3"/>
+    </row>
+    <row r="14" ht="30" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F14" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="G14" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="I14" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="3"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="7"/>
-      <c r="M4" s="7"/>
-      <c r="N4" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="O4" s="3"/>
-    </row>
-    <row r="5" ht="30" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B5" s="2" t="s">
+      <c r="J14" s="5">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3"/>
+      <c r="L14" s="6">
+        <v>46245</v>
+      </c>
+      <c r="M14" s="6">
+        <v>46246</v>
+      </c>
+      <c r="N14" s="6"/>
+      <c r="O14" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="P14" s="3"/>
+    </row>
+    <row r="15" ht="30" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="E15" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="H5" s="3" t="s">
+      <c r="F15" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="J15" s="5">
+        <v>0</v>
+      </c>
+      <c r="K15" s="3"/>
+      <c r="L15" s="6"/>
+      <c r="M15" s="6"/>
+      <c r="N15" s="6"/>
+      <c r="O15" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="P15" s="3"/>
+    </row>
+    <row r="16" ht="30" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="3"/>
-      <c r="K5" s="7"/>
-      <c r="L5" s="7"/>
-      <c r="M5" s="7"/>
-      <c r="N5" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="O5" s="3"/>
-    </row>
-    <row r="6" ht="30" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="H6" s="3" t="s">
+      <c r="J16" s="5">
+        <v>0</v>
+      </c>
+      <c r="K16" s="3"/>
+      <c r="L16" s="6">
+        <v>46266</v>
+      </c>
+      <c r="M16" s="6">
+        <v>46270</v>
+      </c>
+      <c r="N16" s="6"/>
+      <c r="O16" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" ht="30" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="I6" s="5">
-        <v>0</v>
-      </c>
-      <c r="J6" s="3"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="7"/>
-      <c r="M6" s="7"/>
-      <c r="N6" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="O6" s="3"/>
-    </row>
-    <row r="7" ht="30" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="H7" s="3" t="s">
+      <c r="J17" s="5">
+        <v>0</v>
+      </c>
+      <c r="K17" s="3"/>
+      <c r="L17" s="6">
+        <v>46273</v>
+      </c>
+      <c r="M17" s="6">
+        <v>46277</v>
+      </c>
+      <c r="N17" s="6"/>
+      <c r="O17" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="P17" s="3"/>
+    </row>
+    <row r="18" ht="30" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="I7" s="5">
-        <v>0</v>
-      </c>
-      <c r="J7" s="3"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="7"/>
-      <c r="M7" s="7"/>
-      <c r="N7" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="O7" s="3"/>
-    </row>
-    <row r="8" ht="30" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="H8" s="3" t="s">
+      <c r="J18" s="5">
+        <v>0</v>
+      </c>
+      <c r="K18" s="3"/>
+      <c r="L18" s="6">
+        <v>46280</v>
+      </c>
+      <c r="M18" s="6">
+        <v>46291</v>
+      </c>
+      <c r="N18" s="6"/>
+      <c r="O18" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="P18" s="3"/>
+    </row>
+    <row r="19" ht="30" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="I8" s="5">
-        <v>0</v>
-      </c>
-      <c r="J8" s="3"/>
-      <c r="K8" s="7"/>
-      <c r="L8" s="7"/>
-      <c r="M8" s="7"/>
-      <c r="N8" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="O8" s="3"/>
-    </row>
-    <row r="9" ht="30" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="H9" s="3" t="s">
+      <c r="J19" s="5">
+        <v>0</v>
+      </c>
+      <c r="K19" s="3"/>
+      <c r="L19" s="6">
+        <v>46294</v>
+      </c>
+      <c r="M19" s="6">
+        <v>46298</v>
+      </c>
+      <c r="N19" s="6"/>
+      <c r="O19" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" ht="30" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="I20" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="I9" s="5">
-        <v>0</v>
-      </c>
-      <c r="J9" s="3"/>
-      <c r="K9" s="7"/>
-      <c r="L9" s="7"/>
-      <c r="M9" s="7"/>
-      <c r="N9" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="O9" s="3"/>
-    </row>
-    <row r="10" ht="30" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="H10" s="3" t="s">
+      <c r="J20" s="5">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3"/>
+      <c r="L20" s="6">
+        <v>46301</v>
+      </c>
+      <c r="M20" s="6">
+        <v>46305</v>
+      </c>
+      <c r="N20" s="6"/>
+      <c r="O20" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="P20" s="3"/>
+    </row>
+    <row r="21" ht="30" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="I21" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="I10" s="5">
-        <v>0</v>
-      </c>
-      <c r="J10" s="3"/>
-      <c r="K10" s="7"/>
-      <c r="L10" s="7"/>
-      <c r="M10" s="7"/>
-      <c r="N10" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="O10" s="3"/>
-    </row>
-    <row r="11" ht="30" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="H11" s="3" t="s">
+      <c r="J21" s="5">
+        <v>0</v>
+      </c>
+      <c r="K21" s="3"/>
+      <c r="L21" s="6">
+        <v>46308</v>
+      </c>
+      <c r="M21" s="6">
+        <v>46312</v>
+      </c>
+      <c r="N21" s="6"/>
+      <c r="O21" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="P21" s="3"/>
+    </row>
+    <row r="22" ht="30" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="I22" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="I11" s="5">
-        <v>0</v>
-      </c>
-      <c r="J11" s="3"/>
-      <c r="K11" s="7"/>
-      <c r="L11" s="7"/>
-      <c r="M11" s="7"/>
-      <c r="N11" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="O11" s="3"/>
-    </row>
-    <row r="12" ht="30" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="H12" s="3" t="s">
+      <c r="J22" s="5">
+        <v>0</v>
+      </c>
+      <c r="K22" s="3"/>
+      <c r="L22" s="6">
+        <v>46315</v>
+      </c>
+      <c r="M22" s="6">
+        <v>46319</v>
+      </c>
+      <c r="N22" s="6"/>
+      <c r="O22" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="P22" s="3"/>
+    </row>
+    <row r="23" ht="30" customHeight="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="I23" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="I12" s="5">
-        <v>0</v>
-      </c>
-      <c r="J12" s="3"/>
-      <c r="K12" s="7"/>
-      <c r="L12" s="7"/>
-      <c r="M12" s="7"/>
-      <c r="N12" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="O12" s="3"/>
-    </row>
-    <row r="13" ht="30" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I13" s="5">
-        <v>0</v>
-      </c>
-      <c r="J13" s="3"/>
-      <c r="K13" s="7"/>
-      <c r="L13" s="7"/>
-      <c r="M13" s="7"/>
-      <c r="N13" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="O13" s="3"/>
-    </row>
-    <row r="14" ht="30" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I14" s="5">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3"/>
-      <c r="K14" s="7"/>
-      <c r="L14" s="7"/>
-      <c r="M14" s="7"/>
-      <c r="N14" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="O14" s="3"/>
-    </row>
-    <row r="15" ht="30" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="I15" s="5">
-        <v>0</v>
-      </c>
-      <c r="J15" s="3"/>
-      <c r="K15" s="7"/>
-      <c r="L15" s="7"/>
-      <c r="M15" s="7"/>
-      <c r="N15" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="O15" s="3"/>
-    </row>
-    <row r="16" ht="30" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I16" s="5">
-        <v>0</v>
-      </c>
-      <c r="J16" s="3"/>
-      <c r="K16" s="7"/>
-      <c r="L16" s="7"/>
-      <c r="M16" s="7"/>
-      <c r="N16" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="O16" s="3"/>
-    </row>
-    <row r="17" ht="30" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I17" s="5">
-        <v>0</v>
-      </c>
-      <c r="J17" s="3"/>
-      <c r="K17" s="7"/>
-      <c r="L17" s="7"/>
-      <c r="M17" s="7"/>
-      <c r="N17" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="O17" s="3"/>
-    </row>
-    <row r="18" ht="30" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I18" s="5">
-        <v>0</v>
-      </c>
-      <c r="J18" s="3"/>
-      <c r="K18" s="7"/>
-      <c r="L18" s="7"/>
-      <c r="M18" s="7"/>
-      <c r="N18" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="O18" s="3"/>
-    </row>
-    <row r="19" ht="30" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I19" s="5">
-        <v>0</v>
-      </c>
-      <c r="J19" s="3"/>
-      <c r="K19" s="7"/>
-      <c r="L19" s="7"/>
-      <c r="M19" s="7"/>
-      <c r="N19" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="O19" s="3"/>
-    </row>
-    <row r="20" ht="30" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I20" s="5">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3"/>
-      <c r="K20" s="7"/>
-      <c r="L20" s="7"/>
-      <c r="M20" s="7"/>
-      <c r="N20" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="O20" s="3"/>
-    </row>
-    <row r="21" ht="30" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="D21" s="3" t="s">
+      <c r="J23" s="5">
+        <v>0</v>
+      </c>
+      <c r="K23" s="3"/>
+      <c r="L23" s="6"/>
+      <c r="M23" s="6"/>
+      <c r="N23" s="6"/>
+      <c r="O23" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="E21" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I21" s="5">
-        <v>0</v>
-      </c>
-      <c r="J21" s="3"/>
-      <c r="K21" s="7"/>
-      <c r="L21" s="7"/>
-      <c r="M21" s="7"/>
-      <c r="N21" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="O21" s="3"/>
-    </row>
-    <row r="22" ht="30" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I22" s="5">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3"/>
-      <c r="K22" s="7"/>
-      <c r="L22" s="7"/>
-      <c r="M22" s="7"/>
-      <c r="N22" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="O22" s="3"/>
-    </row>
-    <row r="23" ht="30" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I23" s="5">
-        <v>0</v>
-      </c>
-      <c r="J23" s="3"/>
-      <c r="K23" s="7"/>
-      <c r="L23" s="7"/>
-      <c r="M23" s="7"/>
-      <c r="N23" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="O23" s="3"/>
+      <c r="P23" s="3"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O1"/>
-  <conditionalFormatting sqref="L2:L23">
+  <autoFilter ref="A1:P1"/>
+  <conditionalFormatting sqref="M2:M23">
     <cfRule type="expression" dxfId="0" priority="1">
-      <formula>AND($L2&lt;&gt;"",$L2&lt;TODAY(),$H2&lt;&gt;"Done")</formula>
+      <formula>AND($M2&lt;&gt;"",$M2&lt;TODAY(),$I2&lt;&gt;"Done")</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="8">
+  <dataValidations count="10">
     <dataValidation type="list" allowBlank="1" sqref="E10:E23">
       <formula1>"Ops,QA,Eng,Legal,UI,Product"</formula1>
     </dataValidation>
@@ -1888,9 +2084,15 @@
       <formula1>"Yes,No"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="H10:H23">
+      <formula1>"Yes,No,Fast-follow"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="H2:H23">
+      <formula1>"Yes,No,Fast-follow"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="I10:I23">
       <formula1>"Not started,In progress,Blocked,Done"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="H2:H23">
+    <dataValidation type="list" allowBlank="1" sqref="I2:I23">
       <formula1>"Not started,In progress,Blocked,Done"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1901,115 +2103,131 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="2" width="70" customWidth="1"/>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="2" max="2" width="72" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="2" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="8" t="s">
+        <v>119</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="3" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="3" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="4" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="5" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="5" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="6" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="6" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="7" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="7" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>126</v>
-      </c>
       <c r="B7" s="3" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="8" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="8" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="9" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="9" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
+      <c r="B9" s="3" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="10" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="10" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
+      <c r="B10" s="3" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="11" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="11" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>131</v>
-      </c>
       <c r="B11" s="3" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="12" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="12" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="13" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="13" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>136</v>
+        <v>138</v>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="15" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>142</v>
       </c>
     </row>
   </sheetData>
